--- a/2022 data/excel_outputs/12_boothwise_data.xlsx
+++ b/2022 data/excel_outputs/12_boothwise_data.xlsx
@@ -14,795 +14,954 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="396" uniqueCount="287">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="340">
   <si>
     <t>AC 12 Booth-wise Data</t>
   </si>
   <si>
+    <t>Unnamed: 1</t>
+  </si>
+  <si>
+    <t>Unnamed: 2</t>
+  </si>
+  <si>
+    <t>Unnamed: 3</t>
+  </si>
+  <si>
+    <t>Unnamed: 4</t>
+  </si>
+  <si>
+    <t>Unnamed: 5</t>
+  </si>
+  <si>
+    <t>Unnamed: 6</t>
+  </si>
+  <si>
+    <t>Unnamed: 7</t>
+  </si>
+  <si>
+    <t>Unnamed: 8</t>
+  </si>
+  <si>
+    <t>Unnamed: 9</t>
+  </si>
+  <si>
+    <t>Unnamed: 10</t>
+  </si>
+  <si>
+    <t>Unnamed: 11</t>
+  </si>
+  <si>
+    <t>Unnamed: 12</t>
+  </si>
+  <si>
+    <t>Unnamed: 13</t>
+  </si>
+  <si>
+    <t>Unnamed: 14</t>
+  </si>
+  <si>
+    <t>Unnamed: 15</t>
+  </si>
+  <si>
+    <t>Unnamed: 16</t>
+  </si>
+  <si>
+    <t>Unnamed: 17</t>
+  </si>
+  <si>
+    <t>Unnamed: 18</t>
+  </si>
+  <si>
+    <t>Unnamed: 19</t>
+  </si>
+  <si>
+    <t>Unnamed: 20</t>
+  </si>
+  <si>
+    <t>Unnamed: 21</t>
+  </si>
+  <si>
+    <t>Unnamed: 22</t>
+  </si>
+  <si>
+    <t>Unnamed: 23</t>
+  </si>
+  <si>
+    <t>Unnamed: 24</t>
+  </si>
+  <si>
+    <t>Unnamed: 25</t>
+  </si>
+  <si>
     <t>BOOTH ID</t>
   </si>
   <si>
     <t>POLLING STATION NAME</t>
   </si>
   <si>
-    <t>######## ####### ######## #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ####### ######## #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ####### ######## #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ####### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### ### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ########### ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ########### ######## #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ########### ######## #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ########### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ########### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ####### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ######## ####### #### #### 3</t>
-  </si>
-  <si>
-    <t>######## ######## #### ####### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## #### ####### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ######## #### ####### #### #### 3</t>
-  </si>
-  <si>
-    <t>######## ######## #### ####### #### #### 4</t>
-  </si>
-  <si>
-    <t>#### ######## ###### ##### ######## ######## #### ####### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ######### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ######### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ###### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ###### #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ########## #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ########## #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### #### 3</t>
-  </si>
-  <si>
-    <t>######## ######## ##0nn2 ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ##0nn2 ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ######## ######### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh #### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ######## #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ### ### ####### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ### ### ####### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ######## ### ### ####### #### #### 3</t>
-  </si>
-  <si>
-    <t>######## ######## ### ### ####### #### #### 4</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### #### #### 4</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### #### #### 5</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### #### #### 6</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### #### #### 7</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### #### #### 8</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ####### #### #### 9</t>
-  </si>
-  <si>
-    <t>######## ####### ;1.5ddh ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ####### ;1.5ddh ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ####### ;1.5ddh ##### #### #### 3</t>
-  </si>
-  <si>
-    <t>######## ####### ;1.5ddh ##### #### #### 4</t>
-  </si>
-  <si>
-    <t>######## ####### #### 2 ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ####### ########## #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ####### ########## #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ##### #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ##### ### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ##### ### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ##### ### #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ######## #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ######## #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ######## #### #### 4</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ######## #### #### 5</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ######## #### #### 6</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ###### ### ###### #### #### 8</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ###### ### ###### #### #### 9</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ###### ### ###### #### #### 10</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ##### ###### ##### #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ##### ###### ##### #### #### 4</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ##### ###### ##### #### #### 5</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ##### ###### ##### #### #### 7</t>
-  </si>
-  <si>
-    <t>######## ####### ######## #### ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ####### ##### #### ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ######## ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>####### ##### ##### ###### ### ###### #### #### 2</t>
-  </si>
-  <si>
-    <t>####### ##### ##### ###### ### ###### #### #### 4</t>
-  </si>
-  <si>
-    <t>####### ##### ##### ###### ### ###### #### #### 5</t>
-  </si>
-  <si>
-    <t>####### ##### ##### ###### ### ###### #### #### 9</t>
-  </si>
-  <si>
-    <t>####### ##### ##### ###### ### ###### #### #### 10</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ###### ### ###### #### #### 11</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ###### ### ###### #### #### 14</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ###### ### ###### #### #### 13</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ###### ### ###### #### #### 19</t>
-  </si>
-  <si>
-    <t>##### ###### ##### ##### ###### ### ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>##### ###### ##### ##### ###### ### ###### #### #### 2</t>
-  </si>
-  <si>
-    <t>##### ###### ##### ##### ###### ### ###### #### #### 4</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ##### ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ##### ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ##### ##### #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ##### ##### #### #### 4</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh #### #### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh #### #### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ###### #### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ###### #### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ######## #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ###### ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ###### ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ###### ##### #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ###### ##### #### #### 4</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ###### ##### #### #### 5</t>
-  </si>
-  <si>
-    <t>######## ######## #### ######## #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## #### ######## #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ########### #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ########### #### #### 4</t>
-  </si>
-  <si>
-    <t>######## ########e ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ####### #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh #### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh #### #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh #### #### #### 4</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### #### 3</t>
-  </si>
-  <si>
-    <t>######## ######## ###### #### #### 4</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##### #### #### #### 3</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##### #### #### #### 16</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##### #### #### #### 19</t>
-  </si>
-  <si>
-    <t>##### ##### ##### ##### #### #### #### 21</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.1 #### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.1 #### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8 ddh ##### ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8 ddh ##### ###### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8 ddh ##### ###### #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8 ddh ##### ###### #### #### 4</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8 ddh ##### ###### #### #### 5</t>
-  </si>
-  <si>
-    <t>######## ######## ##nn.1 ####### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ##nn.1 ####### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.2 ####### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.2 ####### #### #### 2</t>
-  </si>
-  <si>
-    <t>##### ##### ###### #### #### #### 1#</t>
-  </si>
-  <si>
-    <t>######## ####### ###### #### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ####### ###### #### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ########## #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ########## #### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ####### ########## #### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ####### ########## #### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.2 ###### #### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.2 ###### #### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.2 ###### #### #### #### 3</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.2 ###### #### #### #### 4</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.1 ###### #### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.1 ###### #### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### #### 3</t>
-  </si>
-  <si>
-    <t>######## ######## #### #### #### 4</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ######## #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ######## #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ######## ##### #### #### 4</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ########## #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.1 ########## #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.1 ########## #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######### ####### ;1.8ddh ####### ####### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######### ####### ;1.8ddh ####### ####### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######### ####### ;1.8ddh ####### ####### #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ######### ####### ;1.8ddh ####### ####### #### #### 4</t>
-  </si>
-  <si>
-    <t>######## ########e ##### #### #### #### #### 1</t>
-  </si>
-  <si>
-    <t>########## ##### ##### #### #### #### 1</t>
-  </si>
-  <si>
-    <t>########## ##### ##### #### #### #### 2</t>
-  </si>
-  <si>
-    <t>########## ##### ##### #### #### #### 3</t>
-  </si>
-  <si>
-    <t>########## ##### ##### #### #### #### 4</t>
-  </si>
-  <si>
-    <t>########## ##### ##### #### #### #### 5</t>
-  </si>
-  <si>
-    <t>########## ##### ##### #### #### #### 6</t>
-  </si>
-  <si>
-    <t>###### ######### ###### ##### #### #### #### 1</t>
-  </si>
-  <si>
-    <t>###### ######### ###### ##### #### #### #### 2</t>
-  </si>
-  <si>
-    <t>###### ######### ###### ##### #### #### #### 3</t>
-  </si>
-  <si>
-    <t>###### ######### ###### ##### #### #### #### 4</t>
-  </si>
-  <si>
-    <t>###### ######### ###### ##### #### #### #### 5</t>
-  </si>
-  <si>
-    <t>###### ######### ###### ##### #### #### #### 6</t>
-  </si>
-  <si>
-    <t>######## ####### ######### #### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ####### ######### #### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ########e #########e #### #### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ######## ###### ##### #### #### 3</t>
-  </si>
-  <si>
-    <t>######## ####### ##### ##0 2 #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ####### ##### ##0 2 #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ####### ##### ##0 2 #### #### 3</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.1 ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.1 ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.1 ##### #### #### 3</t>
-  </si>
-  <si>
-    <t>######## ####### ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ####### ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ####### ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ####### ##### #### #### 3</t>
-  </si>
-  <si>
-    <t>######## ######## ##0.2 ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ###### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ###### #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ##### ##### ###### #### #### 4</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ########## ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ########## ###### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ########## ###### #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ########## ###### #### #### 4</t>
-  </si>
-  <si>
-    <t>##### ###### ###### ### ##### ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>##### ###### ###### ### ##### ###### #### #### 2</t>
-  </si>
-  <si>
-    <t>######### ##### ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>######### ##### ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>######### ##### ##### #### #### 3</t>
-  </si>
-  <si>
-    <t>######### ##### ##### #### #### 4</t>
-  </si>
-  <si>
-    <t>######### ##### ##### #### #### 5</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ####### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ####### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ####### ### ####### #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ### ######### #### #### 1</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ##### #### #### 3</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ##### #### #### 4</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ##### #### #### 5</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ##### #### #### 6</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ##### #### #### 7</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ##### #### #### 8</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ##### #### #### 9</t>
-  </si>
-  <si>
-    <t>##### ##### ###### ##### #### #### 10</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ##### #### #### 4</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ##### #### #### 5</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ##### #### #### 6</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ##### #### #### 7</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ##### #### #### 8</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ##### ;1.8ddh ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ##### ;1.8ddh ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ##### ;1.8ddh ##### #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ##### ;1.8ddh ##### #### #### 4</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ##### ;1.8ddh ##### #### #### 5</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ##### ;1.8ddh ##### #### #### 6</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ##### ;1.8ddh ##### #### #### 7</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ##### ;1.8ddh ##### #### #### 8</t>
-  </si>
-  <si>
-    <t>######## ####### ####.1 ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ####### ####.1 ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ####### ####.2 ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ####### ####.2 ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>###### #### ######## ######## ##### #### #### 1</t>
-  </si>
-  <si>
-    <t>###### #### ######## ######## ##### #### #### 2</t>
-  </si>
-  <si>
-    <t>###### #### ######## ######## ##### #### #### 3</t>
-  </si>
-  <si>
-    <t>########## ##### ##### ### #### #### 1</t>
-  </si>
-  <si>
-    <t>########## ##### ##### ### #### #### 2</t>
-  </si>
-  <si>
-    <t>########## ##### ##### ### #### #### 3</t>
-  </si>
-  <si>
-    <t>########## ##### ##### ### #### #### 4</t>
-  </si>
-  <si>
-    <t>########## ##### ##### ### #### #### 5</t>
-  </si>
-  <si>
-    <t>########## ##### ##### ### #### #### 6</t>
-  </si>
-  <si>
-    <t>########## ##### ##### ### #### #### 7</t>
-  </si>
-  <si>
-    <t>########## ##### ##### ### #### #### 8</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ###### #### ### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1.8ddh ######### #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1.8ddh ######### #### #### 2</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1.8ddh ######### #### #### 3</t>
-  </si>
-  <si>
-    <t>#### ######## ######## ;1.8ddh ######### #### #### 4</t>
-  </si>
-  <si>
-    <t>######## ######## ########## #### #### 1</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ###### #### #### 4</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ###### #### #### 5</t>
-  </si>
-  <si>
-    <t>#### ######## ####### ;1.8ddh ###### #### #### 6</t>
-  </si>
-  <si>
-    <t>###### ##e ######### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## #### 2 ###### #### #### 1</t>
-  </si>
-  <si>
-    <t>######## ######## #### 2 ###### #### #### 2</t>
-  </si>
-  <si>
-    <t>######## ######## #### 2 ###### #### #### 3</t>
+    <t>PRATHAMIKA VI0 HOSHIAYARAPURA MAJARA BADHARIRAKHURDA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADADADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADADADADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA ALIPURA</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NO 1 BADH</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADA DADADADA DADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA GYANAMAJRA (RAJPUTAN)</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA GUNIAJUDDI</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADADADADADA DADADADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA MANGANPUR</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA HARNAKI</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>SHAHEED PURANSINGH SMARAK PURV MADHYAMIK VIDYALAYA RONI HARJIPUR</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA BHAMELA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADA DADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADA DADADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADA DADADADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 1 SIKANDARPUR</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 2 SIKANDARPUR</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA PURVI BHAG KANHAHEDI</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA PASCHIMI BHAG KANHAHEDI</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA NUMBER 2 NAYA BHAWAN KAMRA NUMBER 1 DUDHLI</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA ALAMGIRPUR</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA NAYA BHAWAN KAMRA NUMBER 1 KUTESRA</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA NAYA BHAWAN KAMRA NUMBER 2 KUTESRA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>JANTA INTER COLLEGE KAMRA NUMBER 11 KUTESRA</t>
+  </si>
+  <si>
+    <t>JANTA INTER COLLEGE KAMRA NUMBER 17 KUTESRA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA UTTARI BHAG KASOLI</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA UTTARI BHAG SE MILA KAMRA KASOLI</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADA DADADA DADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADA DADADA DADADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADA DADADA DADADADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA NUMBER1 KAMRA NUMBER 2 CHAUKDA</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA NUMBER 2 PURVI BHAG CHAUKDA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADADA DADADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADADA DADADADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADADA DADADADADADADA DADADADA DADADADA 4</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 1 NANGLARAI</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 2 NANGLARAI</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADADA DADADADADADADA DADADADA DADADADA 7</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADADA DADADADADADADA DADADADA DADADADA 8</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADADA DADADADADADADA DADADADA DADADADA 9</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA PASHCHIMI BHAG KA KAMRA NUMBER 2 KULHEDI</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA PASCHIMI KA KAMRA NUMBER 3 KULHEDI</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA ;1.5DDHA DADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA ;1.5DDHA DADADADADA DADADADA DADADADA 4</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 2 KHUSROPUR</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 1 NIRDHANA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADADADADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADADADADADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>ARYA KANYA INTER COLLEGE KAMRA NUMBER 2 CHARTHAWAL DEHAT</t>
+  </si>
+  <si>
+    <t>ARYA KANYA INTER COLLEGE KAMRA NUMBER 3 CHARTHAWAL</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADA DADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADA DADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADA DADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>ARYA KANYA INTER COLLEGE KAMRA NUMBER 7 CHARTHAWAL NAGAR PANCHAYAT</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 1 KISHANURA MAJRA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADADADA DADADADA DADADADA 4</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA BEECH KA KAMRA DALIPPURA MAJRA</t>
+  </si>
+  <si>
+    <t>CHARTHAWAL JAIHIND INTER COLLEGE KAMRA NUMBER 2 CHARTHAWAL NAGAR PANCHAYAT</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>GANDHI INTER COLLEGE KAMRA NUMBER 14 CHARTHAWAL NAGAR PANCHAYAT</t>
+  </si>
+  <si>
+    <t>GANDHI INTER COLLEGE PASCHIMI BHAG KAMRA NUMBER 19 CHARTHAWAL NAGAR PANCHAYAT</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADA DADADADADADA DADADA DADADADADADA DADADADA DADADADA 8</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADA DADADADADADA DADADA DADADADADADA DADADADA DADADADA 9</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADA DADADADADADA DADADA DADADADADADA DADADADA DADADADA 10</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 1 PAVATI</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 2 PAVATI</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADADA DADADADADA DADADADADADA DADADADADA DADADADA DADADADA 5</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADADA DADADADADA DADADADADADA DADADADADA DADADADA DADADADA 7</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA DAKSHINI BHAG BADHAI KALA</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 1 SAIDPUR KALA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADADA DADADADA DADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADADADA DADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 1 SAIDNANGLA</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 2 SAIDNANGLA</t>
+  </si>
+  <si>
+    <t>DADADADADADADA DADADADADA DADADADADA DADADADADADA DADADA DADADADADADA DADADADA DADADADA 5</t>
+  </si>
+  <si>
+    <t>DADADADADADADA DADADADADA DADADADADA DADADADADADA DADADA DADADADADADA DADADADA DADADADA 9</t>
+  </si>
+  <si>
+    <t>DADADADADADADA DADADADADA DADADADADA DADADADADADA DADADA DADADADADADA DADADADA DADADADA 10</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA NUMBER 2 KAMRA NUMBER 1 HAIBATPUR</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA NUMBER 2 KAMRA NUMBER 2 HAIBATPUR</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADA DADADADADADA DADADA DADADADADADA DADADADA DADADADA 13</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADA DADADADADADA DADADA DADADADADADA DADADADA DADADADA 19</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADADA DADADADADA DADADADADA DADADADADADA DADADA DADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 3 BUDINA KHURD</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 4 BUDINAKHURD</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADA DADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADA DADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADA DADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>ISLAMIA MADARSA (SAMNE WALA KAMRA) AMIRNAGAR</t>
+  </si>
+  <si>
+    <t>ISLAMIA MADARSA (DAKSHIN WALA KAMRA) AMIRNAGAR</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADA DADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADA DADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA PURVI BHAG LADWA</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA PURVI BHAG NASIRPUR</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA PURVI BHAG TITAVI</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA PASCHIMI BHAG TITAVI</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADA DADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADA DADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADA DADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>KISAN MAZDOOR INTER COLLEGE KAMRA NUMBER 16 JASOI</t>
+  </si>
+  <si>
+    <t>KISAN MAZDOOR INTER COLLEGE KAMRA NUMBER 19 JASOI</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADA DADADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA GUJJARHEDI</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA PURVI KAMRA NUMBER 1 NAGLA PITHAURA</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA DAKSHINI BHAG KA KAMRA NUMBER 2 PIPALHEDA</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA PURVI BHAG CHATELA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADAE DADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA NUMBER 1 PASCHIMI BHAG SOHJANI</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA NUMBER 2 SOHJANI</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADA DADADADA DADADADA 4</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA NUMBER 1 NAYA BHAWAN PURVI BHAG ALIPUR KALAN</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA NUMBER 1 NAYA BHAWAN PASCHIMI BHAG ALIPUR</t>
+  </si>
+  <si>
+    <t>KANYA PURV MADHYAMIK VIDYALAYA UTTARI BHAG KAMRA NUMBER 1 MOHD PUR MADAN</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA NAYA BHAWAN PURVI BHAG MOHD PUR MADAN</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADA DADADADA DADADADA 4</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA NUMBER 2 WARTMAN KAMRA PURVI BHAG</t>
+  </si>
+  <si>
+    <t>BUDINA KALAN PRATHMIK VIDYALAYA NUMBER 2 ATIRIKT KAKSH NUMBER 1 BUDINA KALAN</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADA DADADADADA DADADADA DADADADA DADADADA 19</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADA DADADADADA DADADADA DADADADA DADADADA 21</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.1 DADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>KALAN PRATHMIK VIDYALAYA DHOLRI</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 1 LAKHAN</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8 DDHA DADADADADA DADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8 DDHA DADADADADA DADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA PURVI BHAG NUNAKHEDA</t>
+  </si>
+  <si>
+    <t>UCCH PRATHMIK VIDYALAYA NUNAKHEDA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8 DDHA DADADADADA DADADADADADA DADADADA DADADADA 5</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA PASCHIMI BHAG DHINDAWALI</t>
+  </si>
+  <si>
+    <t>PRIMARY KANYA PATHSHALA PURVI BHAG KUTBA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADAN.1 DADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>PURVE MADHYAMIK KANYA VIDYALAYA PASHCHIMI BHAG KUTBI</t>
+  </si>
+  <si>
+    <t>PURVE MADHYAMIK KANYA VIDYALAYA BEECH KA KAMRA KUTBI</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.2 DADADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA NUMBER 2 ATRIKT KAKSH HAIDERNAGAR JALAALPUR</t>
+  </si>
+  <si>
+    <t>UCCH PRATHMIK VIDYALAYA HAIDERNAGAR JALALPUR</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADADADADADA DADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>KALYANKARI INTER COLLEGE KAMRA NUMBER 3 BAGHRA</t>
+  </si>
+  <si>
+    <t>KALYANKARI INTER COLLEGE KAMRA NUMBER 4 BAGHRA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADADADADADADADADADA DADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADADADADADADADADADA DADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>SWAMI KALYANDEV DIGREE COLLEGE KAMRA NUMEBR 2 BAGHRA</t>
+  </si>
+  <si>
+    <t>SWAMI KALYANDEV DIGREE COLLEGE KAMRA NUMEBR 3 BAGHRA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.2 DADADADADADA DADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.2 DADADADADADA DADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.2 DADADADADADA DADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 1 BAGHRA</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMEBR 2 BAGHRA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.1 DADADADADADA DADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>KANYA PRATHMIK VIDYALAYA NUMBER 2 DAKSHINI BHAG MANDI</t>
+  </si>
+  <si>
+    <t>KANYA PRATHMIK VIDYALAYA NUMBER 2 UTTARI BHAG ATIRIKT</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADA DADADADA DADADADA 4</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>KANYA PATHSHALA KARWADA</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA PURVI BHAG KHATULA</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMEBR 2 HARSAULI</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 3 HARSAULI</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADA DADADADA DADADADA 4</t>
+  </si>
+  <si>
+    <t>JANTA INTER COLLEGE KAMRA NUMBER 5 HARSAULI</t>
+  </si>
+  <si>
+    <t>JANTA INTER COLLEGE KAMRA NUMBER 6 HARSAULI</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA DADADADADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.1 DADADADADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.1 DADADADADADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA BHUMIAWALA KAMRA NUMBER 4 BARWALA</t>
+  </si>
+  <si>
+    <t>GRAM UTHTHAN JUNIOR HIGH SCHOOL DAKSHINI BHAG KAMRA NUMBER 3 BARWALA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADADA DADADADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADADA DADADADADADADA DADADADA DADADADA 4</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADAE DADADADADA DADADADA DADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 3 TAWLI</t>
+  </si>
+  <si>
+    <t>ISLAMIA SCHOOL KAMRA NUMBER 2 TAWLI</t>
+  </si>
+  <si>
+    <t>DADADADADADADADADADA DADADADADA DADADADADA DADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADADADADADADADA DADADADADA DADADADADA DADADADA DADADADA DADADADA 4</t>
+  </si>
+  <si>
+    <t>DADADADADADADADADADA DADADADADA DADADADADA DADADADA DADADADA DADADADA 5</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA UTTARI BHAG NIRMANI</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA DAKSHINI BHAG NIRMANI</t>
+  </si>
+  <si>
+    <t>DADADADADADA DADADADADADADADADA DADADADADADA DADADADADA DADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADADADA DADADADADADADADADA DADADADADADA DADADADADA DADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADADADA DADADADADADADADADA DADADADADADA DADADADADA DADADADA DADADADA DADADADA 4</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA GADHI DURGANPUR</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 1 MOLAHEDI</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADADADADADADADADA DADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADADADADADADADADA DADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADAE DADADADADADADADADAE DADADADA DADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 3 LACHEDA</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA SIMLI</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADA DADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADADADADA DADA0 2 DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADADADADA DADA0 2 DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>MADARSA FAIZUL ISLAM KAMRA NUMBER 1 SUJDU</t>
+  </si>
+  <si>
+    <t>MADARSA FAIZUL ISLAM KAMRA NUMBER 2 SUJDU</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.1 DADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.1 DADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>MADARSA FAIZUL ISLAM KAMRA NUMBER 6 SUJDU</t>
+  </si>
+  <si>
+    <t>JUNIOR HIGH SCHOOL KAMRA NUMBER 1 SUJDU</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA NUMBER 1 KAMRA NUMBER 3 SUJDU</t>
+  </si>
+  <si>
+    <t>BALIKA UCCH PRATHMIK VIDYALAYA KAMRA NUMBER 1 SUJDU</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADA0.2 DADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADADA DADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA PASCHIMI BHAG VAHALNA</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA UTTARI BHAG VAHALNA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADA DADADADADA DADADADADADA DADADADA DADADADA 4</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADADADADADA DADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADADADADADA DADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA NUMBER 1 KAMRA NUMBER 3 JADAUDA</t>
+  </si>
+  <si>
+    <t>BALIKA UCCH PRATHMIK VIDYALAYA KAMRA NUMBER 1 JADAUDA</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADADA DADADADADADA DADADA DADADADADA DADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADADA DADADADADADA DADADA DADADADADA DADADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>VISHWAKARMA INTER COLLEGE KAMRA NUMBER 1 NARA</t>
+  </si>
+  <si>
+    <t>VISHWAKARMA INTER COLLEGE KAMRA NUMBER 2 NARA</t>
+  </si>
+  <si>
+    <t>DADADADADADADADADA DADADADADA DADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADADA DADADADADA DADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADADADADADADA DADADADADA DADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>PURVE MADHYAMIK VIDYALAYA SANDHAWALI</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 1 SANDHAWALI</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 1 SILA JUDDI</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 1 NAIRANA</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA DADADADADADADA DADADA DADADADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADA DADADADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 1 KHEDIVIRAN</t>
+  </si>
+  <si>
+    <t>PRATHMIK VIDYALAYA KAMRA NUMBER 1 BIHARI</t>
+  </si>
+  <si>
+    <t>3140 0 1 ROOM NO. 299</t>
+  </si>
+  <si>
+    <t>4770 4</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADADA DADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADADA DADADADADA DADADADA DADADADA 4</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADADA DADADADADA DADADADA DADADADA 5</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADADA DADADADADA DADADADA DADADADA 6</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADADA DADADADADA DADADADA DADADADA 9</t>
+  </si>
+  <si>
+    <t>DADADADADA DADADADADA DADADADADADA DADADADADA DADADADA DADADADA 10</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADA DADADADA DADADADA 4</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADA DADADADA DADADADA 5</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADA DADADADA DADADADA 6</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA DADADADADA ;1.8DDHA DADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA DADADADADA ;1.8DDHA DADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA DADADADADA ;1.8DDHA DADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA DADADADADA ;1.8DDHA DADADADADA DADADADA DADADADA 6</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA DADADADADA ;1.8DDHA DADADADADA DADADADA DADADADA 7</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA DADADADADA ;1.8DDHA DADADADADA DADADADA DADADADA 8</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADADADA.1 DADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADA DADADADA.1 DADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADADADA DADADADA DADADADADADADADA DADADADADADADADA DADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADADA DADADADA DADADADADADADADA DADADADADADADADA DADADADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADADADA DADADADA DADADADADADADADA DADADADADADADADA DADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADADADADADADADA DADADADADA DADADADADA DADADA DADADADA DADADADA 2</t>
+  </si>
+  <si>
+    <t>DADADADADADADADADADA DADADADADA DADADADADA DADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADADADADADADADA DADADADADA DADADADADA DADADA DADADADA DADADADA 4</t>
+  </si>
+  <si>
+    <t>DADADADADADADADADADA DADADADADA DADADADADA DADADA DADADADA DADADADA 7</t>
+  </si>
+  <si>
+    <t>DADADADADADADADADADA DADADADADA DADADADADA DADADA DADADADA DADADADA 8</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADA DADADADA DADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADADADA DADADADA DADADADA 5</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1.8DDHA DADADADADADADADADA DADADADA DADADADA 3</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADADA ;1.8DDHA DADADADADADADADADA DADADADA DADADADA 4</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADADADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADA DADADADA DADADADA 4</t>
+  </si>
+  <si>
+    <t>DADADADA DADADADADADADADA DADADADADADADA ;1.8DDHA DADADADADADA DADADADA DADADADA 5</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADA 2 DADADADADADA DADADADA DADADADA 1</t>
+  </si>
+  <si>
+    <t>DADADADADADADADA DADADADADADADADA DADADADA 2 DADADADADADA DADADADA DADADADA 2</t>
   </si>
   <si>
     <t>TOTAL ELECTORS</t>
@@ -881,8 +1040,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="1">
+  <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -898,7 +1065,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -906,12 +1073,30 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1210,88 +1395,163 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:26">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="2" spans="1:26">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>263</v>
+        <v>316</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>317</v>
       </c>
       <c r="E2" t="s">
-        <v>265</v>
+        <v>318</v>
       </c>
       <c r="F2" t="s">
-        <v>266</v>
+        <v>319</v>
       </c>
       <c r="G2" t="s">
-        <v>267</v>
+        <v>320</v>
       </c>
       <c r="H2" t="s">
-        <v>268</v>
+        <v>321</v>
       </c>
       <c r="I2" t="s">
-        <v>269</v>
+        <v>322</v>
       </c>
       <c r="J2" t="s">
-        <v>270</v>
+        <v>323</v>
       </c>
       <c r="K2" t="s">
-        <v>271</v>
+        <v>324</v>
       </c>
       <c r="L2" t="s">
-        <v>272</v>
+        <v>325</v>
       </c>
       <c r="M2" t="s">
-        <v>273</v>
+        <v>326</v>
       </c>
       <c r="N2" t="s">
-        <v>274</v>
+        <v>327</v>
       </c>
       <c r="O2" t="s">
-        <v>275</v>
+        <v>328</v>
       </c>
       <c r="P2" t="s">
-        <v>276</v>
+        <v>329</v>
       </c>
       <c r="Q2" t="s">
-        <v>277</v>
+        <v>330</v>
       </c>
       <c r="R2" t="s">
-        <v>278</v>
+        <v>331</v>
       </c>
       <c r="S2" t="s">
-        <v>279</v>
+        <v>332</v>
       </c>
       <c r="T2" t="s">
-        <v>280</v>
+        <v>333</v>
       </c>
       <c r="U2" t="s">
-        <v>281</v>
+        <v>334</v>
       </c>
       <c r="V2" t="s">
-        <v>282</v>
+        <v>335</v>
       </c>
       <c r="W2" t="s">
-        <v>283</v>
+        <v>336</v>
       </c>
       <c r="X2" t="s">
-        <v>284</v>
+        <v>337</v>
       </c>
       <c r="Y2" t="s">
-        <v>285</v>
+        <v>338</v>
       </c>
       <c r="Z2" t="s">
-        <v>286</v>
+        <v>339</v>
       </c>
     </row>
     <row r="3" spans="1:26">
@@ -1299,7 +1559,7 @@
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="C3">
         <v>1012</v>
@@ -1379,7 +1639,7 @@
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C4">
         <v>1060</v>
@@ -1459,7 +1719,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="C5">
         <v>842</v>
@@ -1539,7 +1799,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="C6">
         <v>936</v>
@@ -1619,7 +1879,7 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>7</v>
+        <v>32</v>
       </c>
       <c r="C7">
         <v>1062</v>
@@ -1699,7 +1959,7 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>8</v>
+        <v>33</v>
       </c>
       <c r="C8">
         <v>414</v>
@@ -1779,7 +2039,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C9">
         <v>616</v>
@@ -1859,7 +2119,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C10">
         <v>635</v>
@@ -1939,7 +2199,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="C11">
         <v>306</v>
@@ -2019,7 +2279,7 @@
         <v>10</v>
       </c>
       <c r="B12" t="s">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="C12">
         <v>606</v>
@@ -2099,7 +2359,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="s">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C13">
         <v>745</v>
@@ -2179,7 +2439,7 @@
         <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C14">
         <v>720</v>
@@ -2259,7 +2519,7 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C15">
         <v>568</v>
@@ -2339,7 +2599,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>6</v>
+        <v>41</v>
       </c>
       <c r="C16">
         <v>685</v>
@@ -2419,7 +2679,7 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="C17">
         <v>779</v>
@@ -2499,7 +2759,7 @@
         <v>16</v>
       </c>
       <c r="B18" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C18">
         <v>913</v>
@@ -2579,7 +2839,7 @@
         <v>17</v>
       </c>
       <c r="B19" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C19">
         <v>940</v>
@@ -2659,7 +2919,7 @@
         <v>18</v>
       </c>
       <c r="B20" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C20">
         <v>887</v>
@@ -2739,7 +2999,7 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>9</v>
+        <v>46</v>
       </c>
       <c r="C21">
         <v>875</v>
@@ -2819,7 +3079,7 @@
         <v>20</v>
       </c>
       <c r="B22" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="C22">
         <v>364</v>
@@ -2899,7 +3159,7 @@
         <v>21</v>
       </c>
       <c r="B23" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="C23">
         <v>1199</v>
@@ -2979,7 +3239,7 @@
         <v>22</v>
       </c>
       <c r="B24" t="s">
-        <v>21</v>
+        <v>49</v>
       </c>
       <c r="C24">
         <v>702</v>
@@ -3059,7 +3319,7 @@
         <v>23</v>
       </c>
       <c r="B25" t="s">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C25">
         <v>683</v>
@@ -3139,7 +3399,7 @@
         <v>24</v>
       </c>
       <c r="B26" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="C26">
         <v>1092</v>
@@ -3219,7 +3479,7 @@
         <v>25</v>
       </c>
       <c r="B27" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="C27">
         <v>1144</v>
@@ -3299,7 +3559,7 @@
         <v>26</v>
       </c>
       <c r="B28" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C28">
         <v>610</v>
@@ -3379,7 +3639,7 @@
         <v>27</v>
       </c>
       <c r="B29" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C29">
         <v>592</v>
@@ -3459,7 +3719,7 @@
         <v>28</v>
       </c>
       <c r="B30" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C30">
         <v>804</v>
@@ -3539,7 +3799,7 @@
         <v>29</v>
       </c>
       <c r="B31" t="s">
-        <v>18</v>
+        <v>55</v>
       </c>
       <c r="C31">
         <v>1049</v>
@@ -3619,7 +3879,7 @@
         <v>30</v>
       </c>
       <c r="B32" t="s">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="C32">
         <v>784</v>
@@ -3699,7 +3959,7 @@
         <v>31</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C33">
         <v>683</v>
@@ -3779,7 +4039,7 @@
         <v>32</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C34">
         <v>678</v>
@@ -3859,7 +4119,7 @@
         <v>33</v>
       </c>
       <c r="B35" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="C35">
         <v>1098</v>
@@ -3939,7 +4199,7 @@
         <v>34</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C36">
         <v>909</v>
@@ -4019,7 +4279,7 @@
         <v>35</v>
       </c>
       <c r="B37" t="s">
-        <v>29</v>
+        <v>59</v>
       </c>
       <c r="C37">
         <v>1146</v>
@@ -4099,7 +4359,7 @@
         <v>36</v>
       </c>
       <c r="B38" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C38">
         <v>1068</v>
@@ -4179,7 +4439,7 @@
         <v>37</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="C39">
         <v>1066</v>
@@ -4259,7 +4519,7 @@
         <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C40">
         <v>1048</v>
@@ -4339,7 +4599,7 @@
         <v>39</v>
       </c>
       <c r="B41" t="s">
-        <v>33</v>
+        <v>63</v>
       </c>
       <c r="C41">
         <v>538</v>
@@ -4419,7 +4679,7 @@
         <v>40</v>
       </c>
       <c r="B42" t="s">
-        <v>9</v>
+        <v>64</v>
       </c>
       <c r="C42">
         <v>494</v>
@@ -4499,7 +4759,7 @@
         <v>41</v>
       </c>
       <c r="B43" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C43">
         <v>958</v>
@@ -4579,7 +4839,7 @@
         <v>42</v>
       </c>
       <c r="B44" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="C44">
         <v>785</v>
@@ -4659,7 +4919,7 @@
         <v>43</v>
       </c>
       <c r="B45" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C45">
         <v>676</v>
@@ -4739,7 +4999,7 @@
         <v>44</v>
       </c>
       <c r="B46" t="s">
-        <v>37</v>
+        <v>68</v>
       </c>
       <c r="C46">
         <v>610</v>
@@ -4819,7 +5079,7 @@
         <v>45</v>
       </c>
       <c r="B47" t="s">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="C47">
         <v>759</v>
@@ -4899,7 +5159,7 @@
         <v>46</v>
       </c>
       <c r="B48" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="C48">
         <v>373</v>
@@ -4979,7 +5239,7 @@
         <v>47</v>
       </c>
       <c r="B49" t="s">
-        <v>40</v>
+        <v>71</v>
       </c>
       <c r="C49">
         <v>1030</v>
@@ -5059,7 +5319,7 @@
         <v>48</v>
       </c>
       <c r="B50" t="s">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="C50">
         <v>693</v>
@@ -5139,7 +5399,7 @@
         <v>49</v>
       </c>
       <c r="B51" t="s">
-        <v>28</v>
+        <v>72</v>
       </c>
       <c r="C51">
         <v>682</v>
@@ -5219,7 +5479,7 @@
         <v>50</v>
       </c>
       <c r="B52" t="s">
-        <v>41</v>
+        <v>73</v>
       </c>
       <c r="C52">
         <v>899</v>
@@ -5299,7 +5559,7 @@
         <v>51</v>
       </c>
       <c r="B53" t="s">
-        <v>42</v>
+        <v>74</v>
       </c>
       <c r="C53">
         <v>957</v>
@@ -5379,7 +5639,7 @@
         <v>52</v>
       </c>
       <c r="B54" t="s">
-        <v>43</v>
+        <v>75</v>
       </c>
       <c r="C54">
         <v>735</v>
@@ -5459,7 +5719,7 @@
         <v>53</v>
       </c>
       <c r="B55" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="C55">
         <v>842</v>
@@ -5539,7 +5799,7 @@
         <v>54</v>
       </c>
       <c r="B56" t="s">
-        <v>45</v>
+        <v>77</v>
       </c>
       <c r="C56">
         <v>798</v>
@@ -5619,7 +5879,7 @@
         <v>55</v>
       </c>
       <c r="B57" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="C57">
         <v>1026</v>
@@ -5699,7 +5959,7 @@
         <v>56</v>
       </c>
       <c r="B58" t="s">
-        <v>47</v>
+        <v>79</v>
       </c>
       <c r="C58">
         <v>1207</v>
@@ -5779,7 +6039,7 @@
         <v>57</v>
       </c>
       <c r="B59" t="s">
-        <v>48</v>
+        <v>80</v>
       </c>
       <c r="C59">
         <v>1084</v>
@@ -5859,7 +6119,7 @@
         <v>58</v>
       </c>
       <c r="B60" t="s">
-        <v>49</v>
+        <v>81</v>
       </c>
       <c r="C60">
         <v>1183</v>
@@ -5939,7 +6199,7 @@
         <v>59</v>
       </c>
       <c r="B61" t="s">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="C61">
         <v>1156</v>
@@ -6019,7 +6279,7 @@
         <v>60</v>
       </c>
       <c r="B62" t="s">
-        <v>51</v>
+        <v>83</v>
       </c>
       <c r="C62">
         <v>830</v>
@@ -6099,7 +6359,7 @@
         <v>61</v>
       </c>
       <c r="B63" t="s">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="C63">
         <v>788</v>
@@ -6179,7 +6439,7 @@
         <v>62</v>
       </c>
       <c r="B64" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="C64">
         <v>1075</v>
@@ -6259,7 +6519,7 @@
         <v>63</v>
       </c>
       <c r="B65" t="s">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="C65">
         <v>935</v>
@@ -6339,7 +6599,7 @@
         <v>64</v>
       </c>
       <c r="B66" t="s">
-        <v>55</v>
+        <v>87</v>
       </c>
       <c r="C66">
         <v>1069</v>
@@ -6419,7 +6679,7 @@
         <v>65</v>
       </c>
       <c r="B67" t="s">
-        <v>56</v>
+        <v>88</v>
       </c>
       <c r="C67">
         <v>980</v>
@@ -6499,7 +6759,7 @@
         <v>66</v>
       </c>
       <c r="B68" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="C68">
         <v>837</v>
@@ -6579,7 +6839,7 @@
         <v>67</v>
       </c>
       <c r="B69" t="s">
-        <v>58</v>
+        <v>90</v>
       </c>
       <c r="C69">
         <v>808</v>
@@ -6659,7 +6919,7 @@
         <v>68</v>
       </c>
       <c r="B70" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C70">
         <v>1176</v>
@@ -6739,7 +6999,7 @@
         <v>69</v>
       </c>
       <c r="B71" t="s">
-        <v>26</v>
+        <v>91</v>
       </c>
       <c r="C71">
         <v>974</v>
@@ -6819,7 +7079,7 @@
         <v>70</v>
       </c>
       <c r="B72" t="s">
-        <v>59</v>
+        <v>92</v>
       </c>
       <c r="C72">
         <v>1061</v>
@@ -6899,7 +7159,7 @@
         <v>71</v>
       </c>
       <c r="B73" t="s">
-        <v>60</v>
+        <v>93</v>
       </c>
       <c r="C73">
         <v>780</v>
@@ -6979,7 +7239,7 @@
         <v>72</v>
       </c>
       <c r="B74" t="s">
-        <v>61</v>
+        <v>94</v>
       </c>
       <c r="C74">
         <v>647</v>
@@ -7059,7 +7319,7 @@
         <v>73</v>
       </c>
       <c r="B75" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C75">
         <v>1088</v>
@@ -7139,7 +7399,7 @@
         <v>74</v>
       </c>
       <c r="B76" t="s">
-        <v>26</v>
+        <v>95</v>
       </c>
       <c r="C76">
         <v>737</v>
@@ -7219,7 +7479,7 @@
         <v>75</v>
       </c>
       <c r="B77" t="s">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="C77">
         <v>580</v>
@@ -7299,7 +7559,7 @@
         <v>76</v>
       </c>
       <c r="B78" t="s">
-        <v>63</v>
+        <v>97</v>
       </c>
       <c r="C78">
         <v>1026</v>
@@ -7379,7 +7639,7 @@
         <v>77</v>
       </c>
       <c r="B79" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="C79">
         <v>1150</v>
@@ -7459,7 +7719,7 @@
         <v>78</v>
       </c>
       <c r="B80" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="C80">
         <v>811</v>
@@ -7539,7 +7799,7 @@
         <v>79</v>
       </c>
       <c r="B81" t="s">
-        <v>27</v>
+        <v>100</v>
       </c>
       <c r="C81">
         <v>1145</v>
@@ -7619,7 +7879,7 @@
         <v>80</v>
       </c>
       <c r="B82" t="s">
-        <v>41</v>
+        <v>101</v>
       </c>
       <c r="C82">
         <v>1159</v>
@@ -7699,7 +7959,7 @@
         <v>81</v>
       </c>
       <c r="B83" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="C83">
         <v>967</v>
@@ -7779,7 +8039,7 @@
         <v>82</v>
       </c>
       <c r="B84" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="C84">
         <v>1179</v>
@@ -7859,7 +8119,7 @@
         <v>83</v>
       </c>
       <c r="B85" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="C85">
         <v>838</v>
@@ -7939,7 +8199,7 @@
         <v>84</v>
       </c>
       <c r="B86" t="s">
-        <v>69</v>
+        <v>105</v>
       </c>
       <c r="C86">
         <v>1233</v>
@@ -8019,7 +8279,7 @@
         <v>85</v>
       </c>
       <c r="B87" t="s">
-        <v>70</v>
+        <v>106</v>
       </c>
       <c r="C87">
         <v>1216</v>
@@ -8099,7 +8359,7 @@
         <v>86</v>
       </c>
       <c r="B88" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="C88">
         <v>764</v>
@@ -8179,7 +8439,7 @@
         <v>87</v>
       </c>
       <c r="B89" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="C89">
         <v>801</v>
@@ -8259,7 +8519,7 @@
         <v>88</v>
       </c>
       <c r="B90" t="s">
-        <v>29</v>
+        <v>108</v>
       </c>
       <c r="C90">
         <v>1203</v>
@@ -8339,7 +8599,7 @@
         <v>89</v>
       </c>
       <c r="B91" t="s">
-        <v>30</v>
+        <v>109</v>
       </c>
       <c r="C91">
         <v>1209</v>
@@ -8419,7 +8679,7 @@
         <v>90</v>
       </c>
       <c r="B92" t="s">
-        <v>31</v>
+        <v>110</v>
       </c>
       <c r="C92">
         <v>1169</v>
@@ -8499,7 +8759,7 @@
         <v>91</v>
       </c>
       <c r="B93" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="C93">
         <v>976</v>
@@ -8579,7 +8839,7 @@
         <v>92</v>
       </c>
       <c r="B94" t="s">
-        <v>72</v>
+        <v>112</v>
       </c>
       <c r="C94">
         <v>919</v>
@@ -8659,7 +8919,7 @@
         <v>93</v>
       </c>
       <c r="B95" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
       <c r="C95">
         <v>659</v>
@@ -8739,7 +8999,7 @@
         <v>94</v>
       </c>
       <c r="B96" t="s">
-        <v>74</v>
+        <v>114</v>
       </c>
       <c r="C96">
         <v>1215</v>
@@ -8819,7 +9079,7 @@
         <v>95</v>
       </c>
       <c r="B97" t="s">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="C97">
         <v>1198</v>
@@ -8899,7 +9159,7 @@
         <v>96</v>
       </c>
       <c r="B98" t="s">
-        <v>76</v>
+        <v>116</v>
       </c>
       <c r="C98">
         <v>1184</v>
@@ -8979,7 +9239,7 @@
         <v>97</v>
       </c>
       <c r="B99" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="C99">
         <v>950</v>
@@ -9059,7 +9319,7 @@
         <v>98</v>
       </c>
       <c r="B100" t="s">
-        <v>77</v>
+        <v>117</v>
       </c>
       <c r="C100">
         <v>1009</v>
@@ -9139,7 +9399,7 @@
         <v>99</v>
       </c>
       <c r="B101" t="s">
-        <v>78</v>
+        <v>118</v>
       </c>
       <c r="C101">
         <v>341</v>
@@ -9219,7 +9479,7 @@
         <v>100</v>
       </c>
       <c r="B102" t="s">
-        <v>79</v>
+        <v>119</v>
       </c>
       <c r="C102">
         <v>342</v>
@@ -9299,7 +9559,7 @@
         <v>101</v>
       </c>
       <c r="B103" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="C103">
         <v>0</v>
@@ -9379,7 +9639,7 @@
         <v>102</v>
       </c>
       <c r="B104" t="s">
-        <v>81</v>
+        <v>121</v>
       </c>
       <c r="C104">
         <v>1011</v>
@@ -9459,7 +9719,7 @@
         <v>103</v>
       </c>
       <c r="B105" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="C105">
         <v>453</v>
@@ -9539,7 +9799,7 @@
         <v>104</v>
       </c>
       <c r="B106" t="s">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="C106">
         <v>1185</v>
@@ -9619,7 +9879,7 @@
         <v>105</v>
       </c>
       <c r="B107" t="s">
-        <v>83</v>
+        <v>123</v>
       </c>
       <c r="C107">
         <v>1105</v>
@@ -9699,7 +9959,7 @@
         <v>106</v>
       </c>
       <c r="B108" t="s">
-        <v>84</v>
+        <v>124</v>
       </c>
       <c r="C108">
         <v>901</v>
@@ -9779,7 +10039,7 @@
         <v>107</v>
       </c>
       <c r="B109" t="s">
-        <v>85</v>
+        <v>125</v>
       </c>
       <c r="C109">
         <v>808</v>
@@ -9859,7 +10119,7 @@
         <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>86</v>
+        <v>126</v>
       </c>
       <c r="C110">
         <v>812</v>
@@ -9939,7 +10199,7 @@
         <v>109</v>
       </c>
       <c r="B111" t="s">
-        <v>87</v>
+        <v>127</v>
       </c>
       <c r="C111">
         <v>993</v>
@@ -10019,7 +10279,7 @@
         <v>110</v>
       </c>
       <c r="B112" t="s">
-        <v>88</v>
+        <v>128</v>
       </c>
       <c r="C112">
         <v>1022</v>
@@ -10099,7 +10359,7 @@
         <v>111</v>
       </c>
       <c r="B113" t="s">
-        <v>89</v>
+        <v>129</v>
       </c>
       <c r="C113">
         <v>1115</v>
@@ -10179,7 +10439,7 @@
         <v>112</v>
       </c>
       <c r="B114" t="s">
-        <v>90</v>
+        <v>130</v>
       </c>
       <c r="C114">
         <v>1107</v>
@@ -10259,7 +10519,7 @@
         <v>113</v>
       </c>
       <c r="B115" t="s">
-        <v>91</v>
+        <v>131</v>
       </c>
       <c r="C115">
         <v>1174</v>
@@ -10339,7 +10599,7 @@
         <v>114</v>
       </c>
       <c r="B116" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="C116">
         <v>1111</v>
@@ -10419,7 +10679,7 @@
         <v>115</v>
       </c>
       <c r="B117" t="s">
-        <v>93</v>
+        <v>133</v>
       </c>
       <c r="C117">
         <v>1096</v>
@@ -10499,7 +10759,7 @@
         <v>116</v>
       </c>
       <c r="B118" t="s">
-        <v>94</v>
+        <v>134</v>
       </c>
       <c r="C118">
         <v>781</v>
@@ -10579,7 +10839,7 @@
         <v>117</v>
       </c>
       <c r="B119" t="s">
-        <v>95</v>
+        <v>135</v>
       </c>
       <c r="C119">
         <v>591</v>
@@ -10659,7 +10919,7 @@
         <v>118</v>
       </c>
       <c r="B120" t="s">
-        <v>96</v>
+        <v>136</v>
       </c>
       <c r="C120">
         <v>746</v>
@@ -10739,7 +10999,7 @@
         <v>119</v>
       </c>
       <c r="B121" t="s">
-        <v>97</v>
+        <v>137</v>
       </c>
       <c r="C121">
         <v>736</v>
@@ -10819,7 +11079,7 @@
         <v>120</v>
       </c>
       <c r="B122" t="s">
-        <v>29</v>
+        <v>138</v>
       </c>
       <c r="C122">
         <v>887</v>
@@ -10899,7 +11159,7 @@
         <v>121</v>
       </c>
       <c r="B123" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C123">
         <v>1180</v>
@@ -10979,7 +11239,7 @@
         <v>122</v>
       </c>
       <c r="B124" t="s">
-        <v>98</v>
+        <v>139</v>
       </c>
       <c r="C124">
         <v>0</v>
@@ -11059,7 +11319,7 @@
         <v>123</v>
       </c>
       <c r="B125" t="s">
-        <v>99</v>
+        <v>140</v>
       </c>
       <c r="C125">
         <v>1151</v>
@@ -11139,7 +11399,7 @@
         <v>124</v>
       </c>
       <c r="B126" t="s">
-        <v>100</v>
+        <v>141</v>
       </c>
       <c r="C126">
         <v>1107</v>
@@ -11219,7 +11479,7 @@
         <v>125</v>
       </c>
       <c r="B127" t="s">
-        <v>101</v>
+        <v>142</v>
       </c>
       <c r="C127">
         <v>819</v>
@@ -11299,7 +11559,7 @@
         <v>126</v>
       </c>
       <c r="B128" t="s">
-        <v>6</v>
+        <v>143</v>
       </c>
       <c r="C128">
         <v>634</v>
@@ -11379,7 +11639,7 @@
         <v>127</v>
       </c>
       <c r="B129" t="s">
-        <v>16</v>
+        <v>144</v>
       </c>
       <c r="C129">
         <v>669</v>
@@ -11459,7 +11719,7 @@
         <v>128</v>
       </c>
       <c r="B130" t="s">
-        <v>6</v>
+        <v>143</v>
       </c>
       <c r="C130">
         <v>841</v>
@@ -11539,7 +11799,7 @@
         <v>129</v>
       </c>
       <c r="B131" t="s">
-        <v>102</v>
+        <v>145</v>
       </c>
       <c r="C131">
         <v>1093</v>
@@ -11619,7 +11879,7 @@
         <v>130</v>
       </c>
       <c r="B132" t="s">
-        <v>103</v>
+        <v>146</v>
       </c>
       <c r="C132">
         <v>799</v>
@@ -11699,7 +11959,7 @@
         <v>131</v>
       </c>
       <c r="B133" t="s">
-        <v>104</v>
+        <v>147</v>
       </c>
       <c r="C133">
         <v>887</v>
@@ -11779,7 +12039,7 @@
         <v>132</v>
       </c>
       <c r="B134" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="C134">
         <v>700</v>
@@ -11859,7 +12119,7 @@
         <v>133</v>
       </c>
       <c r="B135" t="s">
-        <v>106</v>
+        <v>149</v>
       </c>
       <c r="C135">
         <v>797</v>
@@ -11939,7 +12199,7 @@
         <v>134</v>
       </c>
       <c r="B136" t="s">
-        <v>107</v>
+        <v>150</v>
       </c>
       <c r="C136">
         <v>645</v>
@@ -12019,7 +12279,7 @@
         <v>135</v>
       </c>
       <c r="B137" t="s">
-        <v>108</v>
+        <v>151</v>
       </c>
       <c r="C137">
         <v>891</v>
@@ -12099,7 +12359,7 @@
         <v>136</v>
       </c>
       <c r="B138" t="s">
-        <v>6</v>
+        <v>143</v>
       </c>
       <c r="C138">
         <v>0</v>
@@ -12179,7 +12439,7 @@
         <v>137</v>
       </c>
       <c r="B139" t="s">
-        <v>16</v>
+        <v>144</v>
       </c>
       <c r="C139">
         <v>1229</v>
@@ -12259,7 +12519,7 @@
         <v>138</v>
       </c>
       <c r="B140" t="s">
-        <v>109</v>
+        <v>152</v>
       </c>
       <c r="C140">
         <v>967</v>
@@ -12339,7 +12599,7 @@
         <v>139</v>
       </c>
       <c r="B141" t="s">
-        <v>110</v>
+        <v>153</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -12419,7 +12679,7 @@
         <v>140</v>
       </c>
       <c r="B142" t="s">
-        <v>104</v>
+        <v>154</v>
       </c>
       <c r="C142">
         <v>703</v>
@@ -12499,7 +12759,7 @@
         <v>141</v>
       </c>
       <c r="B143" t="s">
-        <v>105</v>
+        <v>148</v>
       </c>
       <c r="C143">
         <v>0</v>
@@ -12579,7 +12839,7 @@
         <v>142</v>
       </c>
       <c r="B144" t="s">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="C144">
         <v>1070</v>
@@ -12659,7 +12919,7 @@
         <v>143</v>
       </c>
       <c r="B145" t="s">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="C145">
         <v>818</v>
@@ -12739,7 +12999,7 @@
         <v>144</v>
       </c>
       <c r="B146" t="s">
-        <v>111</v>
+        <v>155</v>
       </c>
       <c r="C146">
         <v>1112</v>
@@ -12819,7 +13079,7 @@
         <v>145</v>
       </c>
       <c r="B147" t="s">
-        <v>112</v>
+        <v>156</v>
       </c>
       <c r="C147">
         <v>861</v>
@@ -12899,7 +13159,7 @@
         <v>146</v>
       </c>
       <c r="B148" t="s">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c r="C148">
         <v>734</v>
@@ -12979,7 +13239,7 @@
         <v>147</v>
       </c>
       <c r="B149" t="s">
-        <v>6</v>
+        <v>143</v>
       </c>
       <c r="C149">
         <v>1152</v>
@@ -13059,7 +13319,7 @@
         <v>148</v>
       </c>
       <c r="B150" t="s">
-        <v>16</v>
+        <v>144</v>
       </c>
       <c r="C150">
         <v>1088</v>
@@ -13139,7 +13399,7 @@
         <v>149</v>
       </c>
       <c r="B151" t="s">
-        <v>114</v>
+        <v>158</v>
       </c>
       <c r="C151">
         <v>873</v>
@@ -13219,7 +13479,7 @@
         <v>150</v>
       </c>
       <c r="B152" t="s">
-        <v>40</v>
+        <v>159</v>
       </c>
       <c r="C152">
         <v>1093</v>
@@ -13299,7 +13559,7 @@
         <v>151</v>
       </c>
       <c r="B153" t="s">
-        <v>115</v>
+        <v>160</v>
       </c>
       <c r="C153">
         <v>949</v>
@@ -13379,7 +13639,7 @@
         <v>152</v>
       </c>
       <c r="B154" t="s">
-        <v>116</v>
+        <v>161</v>
       </c>
       <c r="C154">
         <v>1057</v>
@@ -13459,7 +13719,7 @@
         <v>153</v>
       </c>
       <c r="B155" t="s">
-        <v>117</v>
+        <v>162</v>
       </c>
       <c r="C155">
         <v>752</v>
@@ -13539,7 +13799,7 @@
         <v>154</v>
       </c>
       <c r="B156" t="s">
-        <v>17</v>
+        <v>163</v>
       </c>
       <c r="C156">
         <v>763</v>
@@ -13619,7 +13879,7 @@
         <v>155</v>
       </c>
       <c r="B157" t="s">
-        <v>18</v>
+        <v>164</v>
       </c>
       <c r="C157">
         <v>733</v>
@@ -13699,7 +13959,7 @@
         <v>156</v>
       </c>
       <c r="B158" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C158">
         <v>604</v>
@@ -13779,7 +14039,7 @@
         <v>157</v>
       </c>
       <c r="B159" t="s">
-        <v>9</v>
+        <v>34</v>
       </c>
       <c r="C159">
         <v>956</v>
@@ -13859,7 +14119,7 @@
         <v>158</v>
       </c>
       <c r="B160" t="s">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="C160">
         <v>702</v>
@@ -13939,7 +14199,7 @@
         <v>159</v>
       </c>
       <c r="B161" t="s">
-        <v>9</v>
+        <v>165</v>
       </c>
       <c r="C161">
         <v>801</v>
@@ -14019,7 +14279,7 @@
         <v>160</v>
       </c>
       <c r="B162" t="s">
-        <v>10</v>
+        <v>166</v>
       </c>
       <c r="C162">
         <v>893</v>
@@ -14099,7 +14359,7 @@
         <v>161</v>
       </c>
       <c r="B163" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="C163">
         <v>1019</v>
@@ -14179,7 +14439,7 @@
         <v>162</v>
       </c>
       <c r="B164" t="s">
-        <v>119</v>
+        <v>168</v>
       </c>
       <c r="C164">
         <v>1170</v>
@@ -14259,7 +14519,7 @@
         <v>163</v>
       </c>
       <c r="B165" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C165">
         <v>1105</v>
@@ -14339,7 +14599,7 @@
         <v>164</v>
       </c>
       <c r="B166" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="C166">
         <v>970</v>
@@ -14419,7 +14679,7 @@
         <v>165</v>
       </c>
       <c r="B167" t="s">
-        <v>121</v>
+        <v>170</v>
       </c>
       <c r="C167">
         <v>958</v>
@@ -14499,7 +14759,7 @@
         <v>166</v>
       </c>
       <c r="B168" t="s">
-        <v>122</v>
+        <v>171</v>
       </c>
       <c r="C168">
         <v>1014</v>
@@ -14579,7 +14839,7 @@
         <v>167</v>
       </c>
       <c r="B169" t="s">
-        <v>123</v>
+        <v>172</v>
       </c>
       <c r="C169">
         <v>873</v>
@@ -14659,7 +14919,7 @@
         <v>168</v>
       </c>
       <c r="B170" t="s">
-        <v>124</v>
+        <v>173</v>
       </c>
       <c r="C170">
         <v>1171</v>
@@ -14739,7 +14999,7 @@
         <v>169</v>
       </c>
       <c r="B171" t="s">
-        <v>125</v>
+        <v>174</v>
       </c>
       <c r="C171">
         <v>1018</v>
@@ -14819,7 +15079,7 @@
         <v>170</v>
       </c>
       <c r="B172" t="s">
-        <v>41</v>
+        <v>175</v>
       </c>
       <c r="C172">
         <v>681</v>
@@ -14899,7 +15159,7 @@
         <v>171</v>
       </c>
       <c r="B173" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="C173">
         <v>668</v>
@@ -14979,7 +15239,7 @@
         <v>172</v>
       </c>
       <c r="B174" t="s">
-        <v>126</v>
+        <v>176</v>
       </c>
       <c r="C174">
         <v>806</v>
@@ -15059,7 +15319,7 @@
         <v>173</v>
       </c>
       <c r="B175" t="s">
-        <v>127</v>
+        <v>177</v>
       </c>
       <c r="C175">
         <v>761</v>
@@ -15139,7 +15399,7 @@
         <v>174</v>
       </c>
       <c r="B176" t="s">
-        <v>128</v>
+        <v>178</v>
       </c>
       <c r="C176">
         <v>711</v>
@@ -15219,7 +15479,7 @@
         <v>175</v>
       </c>
       <c r="B177" t="s">
-        <v>129</v>
+        <v>179</v>
       </c>
       <c r="C177">
         <v>1012</v>
@@ -15299,7 +15559,7 @@
         <v>176</v>
       </c>
       <c r="B178" t="s">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="C178">
         <v>890</v>
@@ -15379,7 +15639,7 @@
         <v>177</v>
       </c>
       <c r="B179" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="C179">
         <v>1081</v>
@@ -15459,7 +15719,7 @@
         <v>178</v>
       </c>
       <c r="B180" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="C180">
         <v>772</v>
@@ -15539,7 +15799,7 @@
         <v>179</v>
       </c>
       <c r="B181" t="s">
-        <v>67</v>
+        <v>181</v>
       </c>
       <c r="C181">
         <v>593</v>
@@ -15619,7 +15879,7 @@
         <v>180</v>
       </c>
       <c r="B182" t="s">
-        <v>25</v>
+        <v>182</v>
       </c>
       <c r="C182">
         <v>1231</v>
@@ -15699,7 +15959,7 @@
         <v>181</v>
       </c>
       <c r="B183" t="s">
-        <v>26</v>
+        <v>54</v>
       </c>
       <c r="C183">
         <v>1073</v>
@@ -15779,7 +16039,7 @@
         <v>182</v>
       </c>
       <c r="B184" t="s">
-        <v>62</v>
+        <v>183</v>
       </c>
       <c r="C184">
         <v>979</v>
@@ -15859,7 +16119,7 @@
         <v>183</v>
       </c>
       <c r="B185" t="s">
-        <v>131</v>
+        <v>184</v>
       </c>
       <c r="C185">
         <v>1104</v>
@@ -15939,7 +16199,7 @@
         <v>184</v>
       </c>
       <c r="B186" t="s">
-        <v>132</v>
+        <v>185</v>
       </c>
       <c r="C186">
         <v>1100</v>
@@ -16019,7 +16279,7 @@
         <v>185</v>
       </c>
       <c r="B187" t="s">
-        <v>133</v>
+        <v>186</v>
       </c>
       <c r="C187">
         <v>748</v>
@@ -16099,7 +16359,7 @@
         <v>186</v>
       </c>
       <c r="B188" t="s">
-        <v>134</v>
+        <v>187</v>
       </c>
       <c r="C188">
         <v>688</v>
@@ -16179,7 +16439,7 @@
         <v>187</v>
       </c>
       <c r="B189" t="s">
-        <v>3</v>
+        <v>188</v>
       </c>
       <c r="C189">
         <v>869</v>
@@ -16259,7 +16519,7 @@
         <v>188</v>
       </c>
       <c r="B190" t="s">
-        <v>4</v>
+        <v>29</v>
       </c>
       <c r="C190">
         <v>921</v>
@@ -16339,7 +16599,7 @@
         <v>189</v>
       </c>
       <c r="B191" t="s">
-        <v>135</v>
+        <v>189</v>
       </c>
       <c r="C191">
         <v>947</v>
@@ -16419,7 +16679,7 @@
         <v>190</v>
       </c>
       <c r="B192" t="s">
-        <v>136</v>
+        <v>190</v>
       </c>
       <c r="C192">
         <v>987</v>
@@ -16499,7 +16759,7 @@
         <v>191</v>
       </c>
       <c r="B193" t="s">
-        <v>137</v>
+        <v>191</v>
       </c>
       <c r="C193">
         <v>952</v>
@@ -16579,7 +16839,7 @@
         <v>192</v>
       </c>
       <c r="B194" t="s">
-        <v>32</v>
+        <v>62</v>
       </c>
       <c r="C194">
         <v>1009</v>
@@ -16659,7 +16919,7 @@
         <v>193</v>
       </c>
       <c r="B195" t="s">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="C195">
         <v>865</v>
@@ -16739,7 +16999,7 @@
         <v>194</v>
       </c>
       <c r="B196" t="s">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="C196">
         <v>791</v>
@@ -16819,7 +17079,7 @@
         <v>195</v>
       </c>
       <c r="B197" t="s">
-        <v>139</v>
+        <v>194</v>
       </c>
       <c r="C197">
         <v>1002</v>
@@ -16899,7 +17159,7 @@
         <v>196</v>
       </c>
       <c r="B198" t="s">
-        <v>140</v>
+        <v>195</v>
       </c>
       <c r="C198">
         <v>881</v>
@@ -16979,7 +17239,7 @@
         <v>197</v>
       </c>
       <c r="B199" t="s">
-        <v>141</v>
+        <v>196</v>
       </c>
       <c r="C199">
         <v>898</v>
@@ -17059,7 +17319,7 @@
         <v>198</v>
       </c>
       <c r="B200" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C200">
         <v>1148</v>
@@ -17139,7 +17399,7 @@
         <v>199</v>
       </c>
       <c r="B201" t="s">
-        <v>34</v>
+        <v>197</v>
       </c>
       <c r="C201">
         <v>771</v>
@@ -17219,7 +17479,7 @@
         <v>200</v>
       </c>
       <c r="B202" t="s">
-        <v>35</v>
+        <v>198</v>
       </c>
       <c r="C202">
         <v>671</v>
@@ -17299,7 +17559,7 @@
         <v>201</v>
       </c>
       <c r="B203" t="s">
-        <v>142</v>
+        <v>199</v>
       </c>
       <c r="C203">
         <v>871</v>
@@ -17379,7 +17639,7 @@
         <v>202</v>
       </c>
       <c r="B204" t="s">
-        <v>143</v>
+        <v>200</v>
       </c>
       <c r="C204">
         <v>760</v>
@@ -17459,7 +17719,7 @@
         <v>203</v>
       </c>
       <c r="B205" t="s">
-        <v>144</v>
+        <v>201</v>
       </c>
       <c r="C205">
         <v>915</v>
@@ -17539,7 +17799,7 @@
         <v>204</v>
       </c>
       <c r="B206" t="s">
-        <v>145</v>
+        <v>202</v>
       </c>
       <c r="C206">
         <v>782</v>
@@ -17619,7 +17879,7 @@
         <v>205</v>
       </c>
       <c r="B207" t="s">
-        <v>146</v>
+        <v>203</v>
       </c>
       <c r="C207">
         <v>671</v>
@@ -17699,7 +17959,7 @@
         <v>206</v>
       </c>
       <c r="B208" t="s">
-        <v>147</v>
+        <v>204</v>
       </c>
       <c r="C208">
         <v>647</v>
@@ -17779,7 +18039,7 @@
         <v>207</v>
       </c>
       <c r="B209" t="s">
-        <v>34</v>
+        <v>65</v>
       </c>
       <c r="C209">
         <v>638</v>
@@ -17859,7 +18119,7 @@
         <v>208</v>
       </c>
       <c r="B210" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="C210">
         <v>665</v>
@@ -17939,7 +18199,7 @@
         <v>209</v>
       </c>
       <c r="B211" t="s">
-        <v>148</v>
+        <v>205</v>
       </c>
       <c r="C211">
         <v>940</v>
@@ -18019,7 +18279,7 @@
         <v>210</v>
       </c>
       <c r="B212" t="s">
-        <v>149</v>
+        <v>206</v>
       </c>
       <c r="C212">
         <v>823</v>
@@ -18099,7 +18359,7 @@
         <v>211</v>
       </c>
       <c r="B213" t="s">
-        <v>150</v>
+        <v>207</v>
       </c>
       <c r="C213">
         <v>820</v>
@@ -18179,7 +18439,7 @@
         <v>212</v>
       </c>
       <c r="B214" t="s">
-        <v>151</v>
+        <v>208</v>
       </c>
       <c r="C214">
         <v>888</v>
@@ -18259,7 +18519,7 @@
         <v>213</v>
       </c>
       <c r="B215" t="s">
-        <v>102</v>
+        <v>209</v>
       </c>
       <c r="C215">
         <v>915</v>
@@ -18339,7 +18599,7 @@
         <v>214</v>
       </c>
       <c r="B216" t="s">
-        <v>152</v>
+        <v>210</v>
       </c>
       <c r="C216">
         <v>1148</v>
@@ -18419,7 +18679,7 @@
         <v>215</v>
       </c>
       <c r="B217" t="s">
-        <v>153</v>
+        <v>211</v>
       </c>
       <c r="C217">
         <v>696</v>
@@ -18499,7 +18759,7 @@
         <v>216</v>
       </c>
       <c r="B218" t="s">
-        <v>41</v>
+        <v>107</v>
       </c>
       <c r="C218">
         <v>1121</v>
@@ -18579,7 +18839,7 @@
         <v>217</v>
       </c>
       <c r="B219" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="C219">
         <v>982</v>
@@ -18659,7 +18919,7 @@
         <v>218</v>
       </c>
       <c r="B220" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="C220">
         <v>959</v>
@@ -18739,7 +18999,7 @@
         <v>219</v>
       </c>
       <c r="B221" t="s">
-        <v>68</v>
+        <v>212</v>
       </c>
       <c r="C221">
         <v>978</v>
@@ -18819,7 +19079,7 @@
         <v>220</v>
       </c>
       <c r="B222" t="s">
-        <v>34</v>
+        <v>213</v>
       </c>
       <c r="C222">
         <v>759</v>
@@ -18899,7 +19159,7 @@
         <v>221</v>
       </c>
       <c r="B223" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="C223">
         <v>672</v>
@@ -18979,7 +19239,7 @@
         <v>222</v>
       </c>
       <c r="B224" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C224">
         <v>679</v>
@@ -19059,7 +19319,7 @@
         <v>223</v>
       </c>
       <c r="B225" t="s">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="C225">
         <v>695</v>
@@ -19139,7 +19399,7 @@
         <v>224</v>
       </c>
       <c r="B226" t="s">
-        <v>25</v>
+        <v>215</v>
       </c>
       <c r="C226">
         <v>1038</v>
@@ -19219,7 +19479,7 @@
         <v>225</v>
       </c>
       <c r="B227" t="s">
-        <v>26</v>
+        <v>216</v>
       </c>
       <c r="C227">
         <v>881</v>
@@ -19299,7 +19559,7 @@
         <v>226</v>
       </c>
       <c r="B228" t="s">
-        <v>155</v>
+        <v>217</v>
       </c>
       <c r="C228">
         <v>875</v>
@@ -19379,7 +19639,7 @@
         <v>227</v>
       </c>
       <c r="B229" t="s">
-        <v>156</v>
+        <v>218</v>
       </c>
       <c r="C229">
         <v>1070</v>
@@ -19459,7 +19719,7 @@
         <v>228</v>
       </c>
       <c r="B230" t="s">
-        <v>157</v>
+        <v>219</v>
       </c>
       <c r="C230">
         <v>964</v>
@@ -19539,7 +19799,7 @@
         <v>229</v>
       </c>
       <c r="B231" t="s">
-        <v>158</v>
+        <v>220</v>
       </c>
       <c r="C231">
         <v>886</v>
@@ -19619,7 +19879,7 @@
         <v>230</v>
       </c>
       <c r="B232" t="s">
-        <v>159</v>
+        <v>221</v>
       </c>
       <c r="C232">
         <v>699</v>
@@ -19699,7 +19959,7 @@
         <v>231</v>
       </c>
       <c r="B233" t="s">
-        <v>160</v>
+        <v>222</v>
       </c>
       <c r="C233">
         <v>699</v>
@@ -19779,7 +20039,7 @@
         <v>232</v>
       </c>
       <c r="B234" t="s">
-        <v>161</v>
+        <v>223</v>
       </c>
       <c r="C234">
         <v>701</v>
@@ -19859,7 +20119,7 @@
         <v>233</v>
       </c>
       <c r="B235" t="s">
-        <v>162</v>
+        <v>224</v>
       </c>
       <c r="C235">
         <v>524</v>
@@ -19939,7 +20199,7 @@
         <v>234</v>
       </c>
       <c r="B236" t="s">
-        <v>163</v>
+        <v>225</v>
       </c>
       <c r="C236">
         <v>1139</v>
@@ -20019,7 +20279,7 @@
         <v>235</v>
       </c>
       <c r="B237" t="s">
-        <v>164</v>
+        <v>226</v>
       </c>
       <c r="C237">
         <v>810</v>
@@ -20099,7 +20359,7 @@
         <v>236</v>
       </c>
       <c r="B238" t="s">
-        <v>165</v>
+        <v>227</v>
       </c>
       <c r="C238">
         <v>1177</v>
@@ -20179,7 +20439,7 @@
         <v>237</v>
       </c>
       <c r="B239" t="s">
-        <v>166</v>
+        <v>228</v>
       </c>
       <c r="C239">
         <v>766</v>
@@ -20259,7 +20519,7 @@
         <v>238</v>
       </c>
       <c r="B240" t="s">
-        <v>167</v>
+        <v>229</v>
       </c>
       <c r="C240">
         <v>961</v>
@@ -20339,7 +20599,7 @@
         <v>239</v>
       </c>
       <c r="B241" t="s">
-        <v>168</v>
+        <v>230</v>
       </c>
       <c r="C241">
         <v>929</v>
@@ -20419,7 +20679,7 @@
         <v>240</v>
       </c>
       <c r="B242" t="s">
-        <v>169</v>
+        <v>231</v>
       </c>
       <c r="C242">
         <v>922</v>
@@ -20499,7 +20759,7 @@
         <v>241</v>
       </c>
       <c r="B243" t="s">
-        <v>170</v>
+        <v>232</v>
       </c>
       <c r="C243">
         <v>880</v>
@@ -20579,7 +20839,7 @@
         <v>242</v>
       </c>
       <c r="B244" t="s">
-        <v>171</v>
+        <v>233</v>
       </c>
       <c r="C244">
         <v>1145</v>
@@ -20659,7 +20919,7 @@
         <v>243</v>
       </c>
       <c r="B245" t="s">
-        <v>172</v>
+        <v>234</v>
       </c>
       <c r="C245">
         <v>875</v>
@@ -20739,7 +20999,7 @@
         <v>244</v>
       </c>
       <c r="B246" t="s">
-        <v>173</v>
+        <v>235</v>
       </c>
       <c r="C246">
         <v>952</v>
@@ -20819,7 +21079,7 @@
         <v>245</v>
       </c>
       <c r="B247" t="s">
-        <v>174</v>
+        <v>236</v>
       </c>
       <c r="C247">
         <v>1002</v>
@@ -20899,7 +21159,7 @@
         <v>246</v>
       </c>
       <c r="B248" t="s">
-        <v>175</v>
+        <v>237</v>
       </c>
       <c r="C248">
         <v>680</v>
@@ -20979,7 +21239,7 @@
         <v>247</v>
       </c>
       <c r="B249" t="s">
-        <v>176</v>
+        <v>238</v>
       </c>
       <c r="C249">
         <v>1102</v>
@@ -21059,7 +21319,7 @@
         <v>248</v>
       </c>
       <c r="B250" t="s">
-        <v>177</v>
+        <v>239</v>
       </c>
       <c r="C250">
         <v>878</v>
@@ -21139,7 +21399,7 @@
         <v>249</v>
       </c>
       <c r="B251" t="s">
-        <v>178</v>
+        <v>240</v>
       </c>
       <c r="C251">
         <v>1209</v>
@@ -21219,7 +21479,7 @@
         <v>250</v>
       </c>
       <c r="B252" t="s">
-        <v>179</v>
+        <v>241</v>
       </c>
       <c r="C252">
         <v>827</v>
@@ -21299,7 +21559,7 @@
         <v>251</v>
       </c>
       <c r="B253" t="s">
-        <v>180</v>
+        <v>242</v>
       </c>
       <c r="C253">
         <v>730</v>
@@ -21379,7 +21639,7 @@
         <v>252</v>
       </c>
       <c r="B254" t="s">
-        <v>181</v>
+        <v>243</v>
       </c>
       <c r="C254">
         <v>1016</v>
@@ -21459,7 +21719,7 @@
         <v>253</v>
       </c>
       <c r="B255" t="s">
-        <v>182</v>
+        <v>244</v>
       </c>
       <c r="C255">
         <v>669</v>
@@ -21539,7 +21799,7 @@
         <v>254</v>
       </c>
       <c r="B256" t="s">
-        <v>183</v>
+        <v>245</v>
       </c>
       <c r="C256">
         <v>667</v>
@@ -21619,7 +21879,7 @@
         <v>255</v>
       </c>
       <c r="B257" t="s">
-        <v>184</v>
+        <v>246</v>
       </c>
       <c r="C257">
         <v>734</v>
@@ -21699,7 +21959,7 @@
         <v>256</v>
       </c>
       <c r="B258" t="s">
-        <v>185</v>
+        <v>247</v>
       </c>
       <c r="C258">
         <v>802</v>
@@ -21779,7 +22039,7 @@
         <v>257</v>
       </c>
       <c r="B259" t="s">
-        <v>186</v>
+        <v>248</v>
       </c>
       <c r="C259">
         <v>1102</v>
@@ -21859,7 +22119,7 @@
         <v>258</v>
       </c>
       <c r="B260" t="s">
-        <v>187</v>
+        <v>249</v>
       </c>
       <c r="C260">
         <v>971</v>
@@ -21939,7 +22199,7 @@
         <v>259</v>
       </c>
       <c r="B261" t="s">
-        <v>188</v>
+        <v>250</v>
       </c>
       <c r="C261">
         <v>1012</v>
@@ -22019,7 +22279,7 @@
         <v>260</v>
       </c>
       <c r="B262" t="s">
-        <v>189</v>
+        <v>251</v>
       </c>
       <c r="C262">
         <v>764</v>
@@ -22099,7 +22359,7 @@
         <v>261</v>
       </c>
       <c r="B263" t="s">
-        <v>190</v>
+        <v>252</v>
       </c>
       <c r="C263">
         <v>725</v>
@@ -22179,7 +22439,7 @@
         <v>262</v>
       </c>
       <c r="B264" t="s">
-        <v>191</v>
+        <v>253</v>
       </c>
       <c r="C264">
         <v>1172</v>
@@ -22259,7 +22519,7 @@
         <v>263</v>
       </c>
       <c r="B265" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C265">
         <v>1046</v>
@@ -22339,7 +22599,7 @@
         <v>264</v>
       </c>
       <c r="B266" t="s">
-        <v>9</v>
+        <v>254</v>
       </c>
       <c r="C266">
         <v>884</v>
@@ -22419,7 +22679,7 @@
         <v>265</v>
       </c>
       <c r="B267" t="s">
-        <v>10</v>
+        <v>255</v>
       </c>
       <c r="C267">
         <v>748</v>
@@ -22499,7 +22759,7 @@
         <v>266</v>
       </c>
       <c r="B268" t="s">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="C268">
         <v>649</v>
@@ -22579,7 +22839,7 @@
         <v>267</v>
       </c>
       <c r="B269" t="s">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="C269">
         <v>928</v>
@@ -22659,7 +22919,7 @@
         <v>268</v>
       </c>
       <c r="B270" t="s">
-        <v>193</v>
+        <v>257</v>
       </c>
       <c r="C270">
         <v>999</v>
@@ -22739,7 +22999,7 @@
         <v>269</v>
       </c>
       <c r="B271" t="s">
-        <v>194</v>
+        <v>258</v>
       </c>
       <c r="C271">
         <v>1034</v>
@@ -22819,7 +23079,7 @@
         <v>270</v>
       </c>
       <c r="B272" t="s">
-        <v>195</v>
+        <v>259</v>
       </c>
       <c r="C272">
         <v>1042</v>
@@ -22899,7 +23159,7 @@
         <v>271</v>
       </c>
       <c r="B273" t="s">
-        <v>196</v>
+        <v>260</v>
       </c>
       <c r="C273">
         <v>1125</v>
@@ -22979,7 +23239,7 @@
         <v>272</v>
       </c>
       <c r="B274" t="s">
-        <v>197</v>
+        <v>261</v>
       </c>
       <c r="C274">
         <v>995</v>
@@ -23059,7 +23319,7 @@
         <v>273</v>
       </c>
       <c r="B275" t="s">
-        <v>198</v>
+        <v>262</v>
       </c>
       <c r="C275">
         <v>905</v>
@@ -23139,7 +23399,7 @@
         <v>274</v>
       </c>
       <c r="B276" t="s">
-        <v>199</v>
+        <v>263</v>
       </c>
       <c r="C276">
         <v>1020</v>
@@ -23219,7 +23479,7 @@
         <v>275</v>
       </c>
       <c r="B277" t="s">
-        <v>200</v>
+        <v>264</v>
       </c>
       <c r="C277">
         <v>1071</v>
@@ -23299,7 +23559,7 @@
         <v>276</v>
       </c>
       <c r="B278" t="s">
-        <v>201</v>
+        <v>265</v>
       </c>
       <c r="C278">
         <v>1006</v>
@@ -23379,7 +23639,7 @@
         <v>277</v>
       </c>
       <c r="B279" t="s">
-        <v>202</v>
+        <v>266</v>
       </c>
       <c r="C279">
         <v>1013</v>
@@ -23459,7 +23719,7 @@
         <v>278</v>
       </c>
       <c r="B280" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C280">
         <v>1068</v>
@@ -23539,7 +23799,7 @@
         <v>279</v>
       </c>
       <c r="B281" t="s">
-        <v>26</v>
+        <v>267</v>
       </c>
       <c r="C281">
         <v>950</v>
@@ -23619,7 +23879,7 @@
         <v>280</v>
       </c>
       <c r="B282" t="s">
-        <v>62</v>
+        <v>268</v>
       </c>
       <c r="C282">
         <v>988</v>
@@ -23699,7 +23959,7 @@
         <v>281</v>
       </c>
       <c r="B283" t="s">
-        <v>203</v>
+        <v>269</v>
       </c>
       <c r="C283">
         <v>932</v>
@@ -23779,7 +24039,7 @@
         <v>282</v>
       </c>
       <c r="B284" t="s">
-        <v>204</v>
+        <v>270</v>
       </c>
       <c r="C284">
         <v>1023</v>
@@ -23859,7 +24119,7 @@
         <v>283</v>
       </c>
       <c r="B285" t="s">
-        <v>205</v>
+        <v>271</v>
       </c>
       <c r="C285">
         <v>713</v>
@@ -23939,7 +24199,7 @@
         <v>284</v>
       </c>
       <c r="B286" t="s">
-        <v>206</v>
+        <v>272</v>
       </c>
       <c r="C286">
         <v>911</v>
@@ -24019,7 +24279,7 @@
         <v>285</v>
       </c>
       <c r="B287" t="s">
-        <v>207</v>
+        <v>273</v>
       </c>
       <c r="C287">
         <v>615</v>
@@ -24099,7 +24359,7 @@
         <v>286</v>
       </c>
       <c r="B288" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C288">
         <v>1058</v>
@@ -24179,7 +24439,7 @@
         <v>287</v>
       </c>
       <c r="B289" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C289">
         <v>1045</v>
@@ -24259,7 +24519,7 @@
         <v>288</v>
       </c>
       <c r="B290" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="C290">
         <v>734</v>
@@ -24339,7 +24599,7 @@
         <v>289</v>
       </c>
       <c r="B291" t="s">
-        <v>208</v>
+        <v>274</v>
       </c>
       <c r="C291">
         <v>925</v>
@@ -24419,7 +24679,7 @@
         <v>290</v>
       </c>
       <c r="B292" t="s">
-        <v>209</v>
+        <v>275</v>
       </c>
       <c r="C292">
         <v>795</v>
@@ -24499,7 +24759,7 @@
         <v>291</v>
       </c>
       <c r="B293" t="s">
-        <v>210</v>
+        <v>276</v>
       </c>
       <c r="C293">
         <v>721</v>
@@ -24579,7 +24839,7 @@
         <v>292</v>
       </c>
       <c r="B294" t="s">
-        <v>211</v>
+        <v>277</v>
       </c>
       <c r="C294">
         <v>1069</v>
@@ -24659,7 +24919,7 @@
         <v>293</v>
       </c>
       <c r="B295" t="s">
-        <v>102</v>
+        <v>209</v>
       </c>
       <c r="C295">
         <v>985</v>
@@ -24739,7 +24999,7 @@
         <v>294</v>
       </c>
       <c r="B296" t="s">
-        <v>103</v>
+        <v>278</v>
       </c>
       <c r="C296">
         <v>840</v>
@@ -24819,7 +25079,7 @@
         <v>295</v>
       </c>
       <c r="B297" t="s">
-        <v>34</v>
+        <v>279</v>
       </c>
       <c r="C297">
         <v>1018</v>
@@ -24899,7 +25159,7 @@
         <v>296</v>
       </c>
       <c r="B298" t="s">
-        <v>35</v>
+        <v>66</v>
       </c>
       <c r="C298">
         <v>1035</v>
@@ -24979,7 +25239,7 @@
         <v>297</v>
       </c>
       <c r="B299" t="s">
-        <v>36</v>
+        <v>67</v>
       </c>
       <c r="C299">
         <v>1024</v>
@@ -25059,7 +25319,7 @@
         <v>298</v>
       </c>
       <c r="B300" t="s">
-        <v>154</v>
+        <v>214</v>
       </c>
       <c r="C300">
         <v>966</v>
@@ -25139,7 +25399,7 @@
         <v>299</v>
       </c>
       <c r="B301" t="s">
-        <v>25</v>
+        <v>280</v>
       </c>
       <c r="C301">
         <v>1203</v>
@@ -25219,7 +25479,7 @@
         <v>300</v>
       </c>
       <c r="B302" t="s">
-        <v>6</v>
+        <v>281</v>
       </c>
       <c r="C302">
         <v>1142</v>
@@ -25299,7 +25559,7 @@
         <v>301</v>
       </c>
       <c r="B303" t="s">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="C303">
         <v>1124</v>
@@ -25379,7 +25639,7 @@
         <v>302</v>
       </c>
       <c r="B304" t="s">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="C304">
         <v>805</v>
@@ -25459,7 +25719,7 @@
         <v>303</v>
       </c>
       <c r="B305" t="s">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="C305">
         <v>745</v>
@@ -25539,7 +25799,7 @@
         <v>304</v>
       </c>
       <c r="B306" t="s">
-        <v>213</v>
+        <v>281</v>
       </c>
       <c r="C306">
         <v>930</v>
@@ -25619,7 +25879,7 @@
         <v>305</v>
       </c>
       <c r="B307" t="s">
-        <v>214</v>
+        <v>281</v>
       </c>
       <c r="C307">
         <v>754</v>
@@ -25699,7 +25959,7 @@
         <v>306</v>
       </c>
       <c r="B308" t="s">
-        <v>215</v>
+        <v>283</v>
       </c>
       <c r="C308">
         <v>667</v>
@@ -25779,7 +26039,7 @@
         <v>307</v>
       </c>
       <c r="B309" t="s">
-        <v>216</v>
+        <v>284</v>
       </c>
       <c r="C309">
         <v>809</v>
@@ -25859,7 +26119,7 @@
         <v>308</v>
       </c>
       <c r="B310" t="s">
-        <v>217</v>
+        <v>285</v>
       </c>
       <c r="C310">
         <v>716</v>
@@ -25939,7 +26199,7 @@
         <v>309</v>
       </c>
       <c r="B311" t="s">
-        <v>218</v>
+        <v>281</v>
       </c>
       <c r="C311">
         <v>1119</v>
@@ -26019,7 +26279,7 @@
         <v>310</v>
       </c>
       <c r="B312" t="s">
-        <v>219</v>
+        <v>281</v>
       </c>
       <c r="C312">
         <v>842</v>
@@ -26099,7 +26359,7 @@
         <v>311</v>
       </c>
       <c r="B313" t="s">
-        <v>220</v>
+        <v>286</v>
       </c>
       <c r="C313">
         <v>1046</v>
@@ -26179,7 +26439,7 @@
         <v>312</v>
       </c>
       <c r="B314" t="s">
-        <v>221</v>
+        <v>287</v>
       </c>
       <c r="C314">
         <v>1014</v>
@@ -26259,7 +26519,7 @@
         <v>313</v>
       </c>
       <c r="B315" t="s">
-        <v>25</v>
+        <v>53</v>
       </c>
       <c r="C315">
         <v>762</v>
@@ -26339,7 +26599,7 @@
         <v>314</v>
       </c>
       <c r="B316" t="s">
-        <v>26</v>
+        <v>281</v>
       </c>
       <c r="C316">
         <v>763</v>
@@ -26419,7 +26679,7 @@
         <v>315</v>
       </c>
       <c r="B317" t="s">
-        <v>62</v>
+        <v>281</v>
       </c>
       <c r="C317">
         <v>777</v>
@@ -26499,7 +26759,7 @@
         <v>316</v>
       </c>
       <c r="B318" t="s">
-        <v>222</v>
+        <v>288</v>
       </c>
       <c r="C318">
         <v>808</v>
@@ -26579,7 +26839,7 @@
         <v>317</v>
       </c>
       <c r="B319" t="s">
-        <v>223</v>
+        <v>289</v>
       </c>
       <c r="C319">
         <v>705</v>
@@ -26659,7 +26919,7 @@
         <v>318</v>
       </c>
       <c r="B320" t="s">
-        <v>224</v>
+        <v>290</v>
       </c>
       <c r="C320">
         <v>682</v>
@@ -26739,7 +26999,7 @@
         <v>319</v>
       </c>
       <c r="B321" t="s">
-        <v>225</v>
+        <v>281</v>
       </c>
       <c r="C321">
         <v>1119</v>
@@ -26819,7 +27079,7 @@
         <v>320</v>
       </c>
       <c r="B322" t="s">
-        <v>226</v>
+        <v>281</v>
       </c>
       <c r="C322">
         <v>808</v>
@@ -26899,7 +27159,7 @@
         <v>321</v>
       </c>
       <c r="B323" t="s">
-        <v>227</v>
+        <v>291</v>
       </c>
       <c r="C323">
         <v>758</v>
@@ -26979,7 +27239,7 @@
         <v>322</v>
       </c>
       <c r="B324" t="s">
-        <v>228</v>
+        <v>292</v>
       </c>
       <c r="C324">
         <v>768</v>
@@ -27059,7 +27319,7 @@
         <v>323</v>
       </c>
       <c r="B325" t="s">
-        <v>229</v>
+        <v>293</v>
       </c>
       <c r="C325">
         <v>760</v>
@@ -27139,7 +27399,7 @@
         <v>324</v>
       </c>
       <c r="B326" t="s">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="C326">
         <v>723</v>
@@ -27219,7 +27479,7 @@
         <v>325</v>
       </c>
       <c r="B327" t="s">
-        <v>231</v>
+        <v>281</v>
       </c>
       <c r="C327">
         <v>858</v>
@@ -27299,7 +27559,7 @@
         <v>326</v>
       </c>
       <c r="B328" t="s">
-        <v>232</v>
+        <v>294</v>
       </c>
       <c r="C328">
         <v>751</v>
@@ -27379,7 +27639,7 @@
         <v>327</v>
       </c>
       <c r="B329" t="s">
-        <v>233</v>
+        <v>295</v>
       </c>
       <c r="C329">
         <v>811</v>
@@ -27459,7 +27719,7 @@
         <v>328</v>
       </c>
       <c r="B330" t="s">
-        <v>234</v>
+        <v>296</v>
       </c>
       <c r="C330">
         <v>1172</v>
@@ -27539,7 +27799,7 @@
         <v>329</v>
       </c>
       <c r="B331" t="s">
-        <v>25</v>
+        <v>281</v>
       </c>
       <c r="C331">
         <v>1119</v>
@@ -27619,7 +27879,7 @@
         <v>330</v>
       </c>
       <c r="B332" t="s">
-        <v>26</v>
+        <v>281</v>
       </c>
       <c r="C332">
         <v>1049</v>
@@ -27699,7 +27959,7 @@
         <v>331</v>
       </c>
       <c r="B333" t="s">
-        <v>62</v>
+        <v>183</v>
       </c>
       <c r="C333">
         <v>1079</v>
@@ -27779,7 +28039,7 @@
         <v>332</v>
       </c>
       <c r="B334" t="s">
-        <v>235</v>
+        <v>297</v>
       </c>
       <c r="C334">
         <v>673</v>
@@ -27859,7 +28119,7 @@
         <v>333</v>
       </c>
       <c r="B335" t="s">
-        <v>236</v>
+        <v>298</v>
       </c>
       <c r="C335">
         <v>957</v>
@@ -27939,7 +28199,7 @@
         <v>334</v>
       </c>
       <c r="B336" t="s">
-        <v>237</v>
+        <v>281</v>
       </c>
       <c r="C336">
         <v>1092</v>
@@ -28019,7 +28279,7 @@
         <v>335</v>
       </c>
       <c r="B337" t="s">
-        <v>238</v>
+        <v>281</v>
       </c>
       <c r="C337">
         <v>1203</v>
@@ -28099,7 +28359,7 @@
         <v>336</v>
       </c>
       <c r="B338" t="s">
-        <v>239</v>
+        <v>299</v>
       </c>
       <c r="C338">
         <v>1042</v>
@@ -28179,7 +28439,7 @@
         <v>337</v>
       </c>
       <c r="B339" t="s">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="C339">
         <v>911</v>
@@ -28259,7 +28519,7 @@
         <v>338</v>
       </c>
       <c r="B340" t="s">
-        <v>241</v>
+        <v>301</v>
       </c>
       <c r="C340">
         <v>1090</v>
@@ -28339,7 +28599,7 @@
         <v>339</v>
       </c>
       <c r="B341" t="s">
-        <v>34</v>
+        <v>281</v>
       </c>
       <c r="C341">
         <v>495</v>
@@ -28419,7 +28679,7 @@
         <v>340</v>
       </c>
       <c r="B342" t="s">
-        <v>242</v>
+        <v>281</v>
       </c>
       <c r="C342">
         <v>933</v>
@@ -28499,7 +28759,7 @@
         <v>341</v>
       </c>
       <c r="B343" t="s">
-        <v>243</v>
+        <v>302</v>
       </c>
       <c r="C343">
         <v>824</v>
@@ -28579,7 +28839,7 @@
         <v>342</v>
       </c>
       <c r="B344" t="s">
-        <v>244</v>
+        <v>303</v>
       </c>
       <c r="C344">
         <v>818</v>
@@ -28659,7 +28919,7 @@
         <v>343</v>
       </c>
       <c r="B345" t="s">
-        <v>245</v>
+        <v>304</v>
       </c>
       <c r="C345">
         <v>749</v>
@@ -28739,7 +28999,7 @@
         <v>344</v>
       </c>
       <c r="B346" t="s">
-        <v>246</v>
+        <v>281</v>
       </c>
       <c r="C346">
         <v>834</v>
@@ -28819,7 +29079,7 @@
         <v>345</v>
       </c>
       <c r="B347" t="s">
-        <v>247</v>
+        <v>281</v>
       </c>
       <c r="C347">
         <v>797</v>
@@ -28899,7 +29159,7 @@
         <v>346</v>
       </c>
       <c r="B348" t="s">
-        <v>248</v>
+        <v>305</v>
       </c>
       <c r="C348">
         <v>685</v>
@@ -28979,7 +29239,7 @@
         <v>347</v>
       </c>
       <c r="B349" t="s">
-        <v>249</v>
+        <v>306</v>
       </c>
       <c r="C349">
         <v>715</v>
@@ -29059,7 +29319,7 @@
         <v>348</v>
       </c>
       <c r="B350" t="s">
-        <v>250</v>
+        <v>307</v>
       </c>
       <c r="C350">
         <v>1189</v>
@@ -29139,7 +29399,7 @@
         <v>349</v>
       </c>
       <c r="B351" t="s">
-        <v>41</v>
+        <v>281</v>
       </c>
       <c r="C351">
         <v>654</v>
@@ -29219,7 +29479,7 @@
         <v>350</v>
       </c>
       <c r="B352" t="s">
-        <v>66</v>
+        <v>281</v>
       </c>
       <c r="C352">
         <v>720</v>
@@ -29299,7 +29559,7 @@
         <v>351</v>
       </c>
       <c r="B353" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="C353">
         <v>991</v>
@@ -29379,7 +29639,7 @@
         <v>352</v>
       </c>
       <c r="B354" t="s">
-        <v>68</v>
+        <v>104</v>
       </c>
       <c r="C354">
         <v>1005</v>
@@ -29459,7 +29719,7 @@
         <v>353</v>
       </c>
       <c r="B355" t="s">
-        <v>69</v>
+        <v>308</v>
       </c>
       <c r="C355">
         <v>869</v>
@@ -29539,7 +29799,7 @@
         <v>354</v>
       </c>
       <c r="B356" t="s">
-        <v>251</v>
+        <v>281</v>
       </c>
       <c r="C356">
         <v>674</v>
@@ -29619,7 +29879,7 @@
         <v>355</v>
       </c>
       <c r="B357" t="s">
-        <v>252</v>
+        <v>281</v>
       </c>
       <c r="C357">
         <v>635</v>
@@ -29699,7 +29959,7 @@
         <v>356</v>
       </c>
       <c r="B358" t="s">
-        <v>253</v>
+        <v>309</v>
       </c>
       <c r="C358">
         <v>655</v>
@@ -29779,7 +30039,7 @@
         <v>357</v>
       </c>
       <c r="B359" t="s">
-        <v>254</v>
+        <v>310</v>
       </c>
       <c r="C359">
         <v>757</v>
@@ -29859,7 +30119,7 @@
         <v>358</v>
       </c>
       <c r="B360" t="s">
-        <v>255</v>
+        <v>311</v>
       </c>
       <c r="C360">
         <v>1196</v>
@@ -29939,7 +30199,7 @@
         <v>359</v>
       </c>
       <c r="B361" t="s">
-        <v>29</v>
+        <v>281</v>
       </c>
       <c r="C361">
         <v>1027</v>
@@ -30019,7 +30279,7 @@
         <v>360</v>
       </c>
       <c r="B362" t="s">
-        <v>30</v>
+        <v>281</v>
       </c>
       <c r="C362">
         <v>763</v>
@@ -30099,7 +30359,7 @@
         <v>361</v>
       </c>
       <c r="B363" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="C363">
         <v>797</v>
@@ -30179,7 +30439,7 @@
         <v>362</v>
       </c>
       <c r="B364" t="s">
-        <v>256</v>
+        <v>312</v>
       </c>
       <c r="C364">
         <v>901</v>
@@ -30259,7 +30519,7 @@
         <v>363</v>
       </c>
       <c r="B365" t="s">
-        <v>257</v>
+        <v>313</v>
       </c>
       <c r="C365">
         <v>764</v>
@@ -30339,7 +30599,7 @@
         <v>364</v>
       </c>
       <c r="B366" t="s">
-        <v>258</v>
+        <v>281</v>
       </c>
       <c r="C366">
         <v>720</v>
@@ -30419,7 +30679,7 @@
         <v>365</v>
       </c>
       <c r="B367" t="s">
-        <v>259</v>
+        <v>281</v>
       </c>
       <c r="C367">
         <v>1113</v>
@@ -30499,7 +30759,7 @@
         <v>366</v>
       </c>
       <c r="B368" t="s">
-        <v>39</v>
+        <v>70</v>
       </c>
       <c r="C368">
         <v>1107</v>
@@ -30579,7 +30839,7 @@
         <v>367</v>
       </c>
       <c r="B369" t="s">
-        <v>260</v>
+        <v>314</v>
       </c>
       <c r="C369">
         <v>909</v>
@@ -30659,7 +30919,7 @@
         <v>368</v>
       </c>
       <c r="B370" t="s">
-        <v>261</v>
+        <v>315</v>
       </c>
       <c r="C370">
         <v>1140</v>
@@ -30739,7 +30999,7 @@
         <v>369</v>
       </c>
       <c r="B371" t="s">
-        <v>262</v>
+        <v>281</v>
       </c>
       <c r="C371">
         <v>1173</v>
